--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/0080-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/0080-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC1AE373-1507-4A90-9653-32A76A4F09E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDA7A36A-4B27-4E24-8413-93C2486D5483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{DB2B62DC-AEEB-4A75-85CA-238BEAD1779E}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{983317F8-8E9D-4BD5-AC3B-B4F5801CF9CD}"/>
   </bookViews>
   <sheets>
     <sheet name="0080-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1475,28 +1475,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F46F2A6-BFAD-4212-869F-7A88A2042190}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01FB4BA-36A0-482C-A438-FC41B45B0DD7}">
   <dimension ref="A1:X24"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="8.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="7" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1530,7 +1530,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1566,7 +1566,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1686,7 +1686,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2015</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2014</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>4.45</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>2.61</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>1.84</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2013</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>1.72</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2012</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>4.7300000000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>1.67</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2011</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>1.76</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2010</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>29</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2009</v>
       </c>
@@ -3004,7 +3004,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37" t="s">
         <v>46</v>
       </c>
